--- a/backend/aws/info.xlsx
+++ b/backend/aws/info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucia\Documents\GitHub\TFG_Posdata\backend\aws\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B73687B-4E17-4573-9BCC-2128429CB66E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B90CD507-6FD8-4851-B5DC-C4E59DD2D7ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{717247B1-5BD0-4CA7-8E56-C22B8892B153}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>AWS Service</t>
   </si>
@@ -96,6 +96,13 @@
   <si>
     <t>Handles dynamic user updates in DynamoDB. Performs schema validation for 
 emergency contacts and accessibility settings, using Attribute Name Aliasing to prevent reserved word collisions and ensuring record existence via Condition Expressions.</t>
+  </si>
+  <si>
+    <t>Handles soft deletion of user accounts in DynamoDB. Validates input identifiers 
+and performs a partial update to set the ACTIVE flag to false. Includes conditional logic to fail gracefully if the targeted User ID is not found in the database.</t>
+  </si>
+  <si>
+    <t>Test cases</t>
   </si>
 </sst>
 </file>
@@ -221,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -238,24 +245,27 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -265,8 +275,8 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -582,16 +592,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC3E1799-8E9C-484C-98AD-CB385F3A2068}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.26953125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="70.08984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="70.90625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="15" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -604,96 +614,101 @@
       <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
+      <c r="E1" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="6"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="8" t="s">
+    <row r="3" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="11"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="6"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="8" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="11"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="10"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="6"/>
-      <c r="B5" s="7" t="s">
+      <c r="D4" s="9"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="11"/>
+      <c r="B5" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="10"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="6"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="8" t="s">
+      <c r="D5" s="9"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="11"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="10"/>
-    </row>
-    <row r="7" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="6"/>
-      <c r="B7" s="12" t="s">
+      <c r="D6" s="9"/>
+    </row>
+    <row r="7" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="11"/>
+      <c r="B7" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A8" s="6"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="8" t="s">
+    <row r="8" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="11"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="6"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="8" t="s">
+    <row r="9" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="11"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="10"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="6"/>
-      <c r="B10" s="11" t="s">
+      <c r="D9" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="11"/>
+      <c r="B10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="10"/>
+      <c r="D10" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/backend/aws/info.xlsx
+++ b/backend/aws/info.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucia\Documents\GitHub\TFG_Posdata\backend\aws\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B90CD507-6FD8-4851-B5DC-C4E59DD2D7ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C00105-3563-4389-9A82-C275E7B4E462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{717247B1-5BD0-4CA7-8E56-C22B8892B153}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{717247B1-5BD0-4CA7-8E56-C22B8892B153}"/>
   </bookViews>
   <sheets>
-    <sheet name="Lambda" sheetId="1" r:id="rId1"/>
+    <sheet name="DynamoDB" sheetId="2" r:id="rId1"/>
+    <sheet name="Lambda" sheetId="1" r:id="rId2"/>
+    <sheet name="S3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="48">
   <si>
     <t>AWS Service</t>
   </si>
@@ -37,9 +39,6 @@
   </si>
   <si>
     <t>Lambda</t>
-  </si>
-  <si>
-    <t>posdata-listssmschech-lambda</t>
   </si>
   <si>
     <t>SMS Verdict Engine: Performs multi-stage validation of incoming messages against
@@ -102,7 +101,83 @@
 and performs a partial update to set the ACTIVE flag to false. Includes conditional logic to fail gracefully if the targeted User ID is not found in the database.</t>
   </si>
   <si>
-    <t>Test cases</t>
+    <t>Automates CSV data ingestion from S3 to DynamoDB. Includes memory-optimized 
+streaming, schema validation, and high-throughput batch writing to ensure efficient data migration and synchronization."</t>
+  </si>
+  <si>
+    <t>Python 3.14</t>
+  </si>
+  <si>
+    <t>Layers</t>
+  </si>
+  <si>
+    <t>posdata-utils-layer v8</t>
+  </si>
+  <si>
+    <t>Trigger</t>
+  </si>
+  <si>
+    <t>Destination</t>
+  </si>
+  <si>
+    <t>posdata-listssmscheck-lambda</t>
+  </si>
+  <si>
+    <t>posdata-hashlearning-queue</t>
+  </si>
+  <si>
+    <t>posdata-smslists-s3</t>
+  </si>
+  <si>
+    <t>Language Version</t>
+  </si>
+  <si>
+    <t>posdata-smslists-db</t>
+  </si>
+  <si>
+    <t>posdata-users-db</t>
+  </si>
+  <si>
+    <t>DynamoDB</t>
+  </si>
+  <si>
+    <t>SMS - Lists update</t>
+  </si>
+  <si>
+    <t>Partition Key</t>
+  </si>
+  <si>
+    <t>Sort Key</t>
+  </si>
+  <si>
+    <t>PK (String)</t>
+  </si>
+  <si>
+    <t>SK (String)</t>
+  </si>
+  <si>
+    <t>ARN</t>
+  </si>
+  <si>
+    <t>arn:aws:dynamodb:eu-west-3:170722810141:table/posdata-smslists-db</t>
+  </si>
+  <si>
+    <t>arn:aws:dynamodb:eu-west-3:170722810141:table/posdata-users-db</t>
+  </si>
+  <si>
+    <t>arn:aws:lambda:eu-west-3:170722810141:function:posdata-updateuser-lambda</t>
+  </si>
+  <si>
+    <t>arn:aws:lambda:eu-west-3:170722810141:function:posdata-listssmscheck-lambda</t>
+  </si>
+  <si>
+    <t>arn:aws:lambda:eu-west-3:170722810141:function:posdata-insertitemsintodynamodb-lambda</t>
+  </si>
+  <si>
+    <t>arn:aws:lambda:eu-west-3:170722810141:function:posdata-deactivate-user</t>
+  </si>
+  <si>
+    <t>arn:aws:lambda:eu-west-3:170722810141:function:posdata-learnhash-lambda</t>
   </si>
 </sst>
 </file>
@@ -126,7 +201,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -163,8 +238,44 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -208,17 +319,6 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -228,7 +328,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -260,23 +360,56 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -284,6 +417,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFCCFF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -591,124 +729,338 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AAE0A43-D9F4-4772-8EF4-455A5F157D98}">
+  <sheetPr>
+    <tabColor theme="4"/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.90625" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.54296875" style="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="61.36328125" style="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="20"/>
+      <c r="B3" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="21"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="20"/>
+      <c r="B4" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="23"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="20"/>
+      <c r="B5" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="21"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="23"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="D4:D5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC3E1799-8E9C-484C-98AD-CB385F3A2068}">
-  <dimension ref="A1:E10"/>
+  <sheetPr>
+    <tabColor theme="5"/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.26953125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="70.90625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="83.36328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="70.90625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="15" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="G2" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+    </row>
+    <row r="3" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="12"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="16"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="12"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="11"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="8" t="s">
+      <c r="D4" s="7"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="12"/>
+      <c r="B5" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="12"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+    </row>
+    <row r="7" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="12"/>
+      <c r="B7" s="13" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="11"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="9"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="9"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="11"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="9"/>
-    </row>
-    <row r="7" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="11"/>
-      <c r="B7" s="13" t="s">
+      <c r="C7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+    </row>
+    <row r="8" spans="1:9" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="12"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+    </row>
+    <row r="9" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="12"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+    </row>
+    <row r="10" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="12"/>
+      <c r="B10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="58" x14ac:dyDescent="0.35">
-      <c r="A8" s="11"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="11"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="7" t="s">
+      <c r="C10" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D10" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="14" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="11"/>
-      <c r="B10" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="9"/>
+      <c r="F10" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -719,4 +1071,16 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1FCA5BB-BB75-4692-B0DF-C8BE087A85D5}">
+  <sheetPr>
+    <tabColor theme="9"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/backend/aws/info.xlsx
+++ b/backend/aws/info.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucia\Documents\GitHub\TFG_Posdata\backend\aws\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C00105-3563-4389-9A82-C275E7B4E462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677EFA6E-5CD0-4B8B-9270-74E54C710522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{717247B1-5BD0-4CA7-8E56-C22B8892B153}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{717247B1-5BD0-4CA7-8E56-C22B8892B153}"/>
   </bookViews>
   <sheets>
-    <sheet name="DynamoDB" sheetId="2" r:id="rId1"/>
-    <sheet name="Lambda" sheetId="1" r:id="rId2"/>
-    <sheet name="S3" sheetId="3" r:id="rId3"/>
+    <sheet name="API Gateway" sheetId="5" r:id="rId1"/>
+    <sheet name="DynamoDB" sheetId="2" r:id="rId2"/>
+    <sheet name="Lambda" sheetId="1" r:id="rId3"/>
+    <sheet name="S3" sheetId="3" r:id="rId4"/>
+    <sheet name="SQS" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="73">
   <si>
     <t>AWS Service</t>
   </si>
@@ -178,13 +180,91 @@
   </si>
   <si>
     <t>arn:aws:lambda:eu-west-3:170722810141:function:posdata-learnhash-lambda</t>
+  </si>
+  <si>
+    <t>posdata-smsresults-s3</t>
+  </si>
+  <si>
+    <t>S3</t>
+  </si>
+  <si>
+    <t>arn:aws:s3:::posdata-smslists-s3</t>
+  </si>
+  <si>
+    <t>posdata-smsmodel-s3</t>
+  </si>
+  <si>
+    <t>arn:aws:s3:::posdata-smsmodel-s3</t>
+  </si>
+  <si>
+    <t>arn:aws:s3:::posdata-smsresults-s3</t>
+  </si>
+  <si>
+    <t>Trained AI detection model.</t>
+  </si>
+  <si>
+    <t>CSV lists to insert in the corresponding DynamoDB.</t>
+  </si>
+  <si>
+    <t>SMS check results to bee gathered by the requester.</t>
+  </si>
+  <si>
+    <t>Content</t>
+  </si>
+  <si>
+    <t>SQS</t>
+  </si>
+  <si>
+    <t>arn:aws:sqs:eu-west-3:170722810141:posdata-hashlearning-queue</t>
+  </si>
+  <si>
+    <t>arn:aws:lambda:eu-west-3:170722810141:function:posdata-aismscheck-lambda</t>
+  </si>
+  <si>
+    <t>Python 3.12</t>
+  </si>
+  <si>
+    <t>AI Inference Service for SMS security. Uses XLM-RoBERTa + ONNX to detect 
+malicious intent in text. Optimized for serverless performance with global model caching and CPU-enabled inference sessions.</t>
+  </si>
+  <si>
+    <t>arn:aws:lambda:eu-west-3:170722810141:function:posdata-notifysmscheck-lambda</t>
+  </si>
+  <si>
+    <t>Orchestrates multi-channel security alerts via SNS (SMS) and SES (Email) while 
+archiving analysis results in S3. Features transactional priority for SMS alerts and detailed HTML reporting for emergency contacts</t>
+  </si>
+  <si>
+    <t>Methods</t>
+  </si>
+  <si>
+    <t>Resources</t>
+  </si>
+  <si>
+    <t>API Gateway</t>
+  </si>
+  <si>
+    <t>posdata-api</t>
+  </si>
+  <si>
+    <t>/sms</t>
+  </si>
+  <si>
+    <t>POST</t>
+  </si>
+  <si>
+    <t>arn:aws:execute-api:eu-west-3:170722810141:w82baca113/*/POST/sms</t>
+  </si>
+  <si>
+    <t>Triggers the SMS check state machine to analyze if the received 
+message is phishing.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -200,8 +280,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -271,6 +359,54 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF33CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF66FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6600CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9966FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC99FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -328,7 +464,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -363,12 +499,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -387,8 +517,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -399,17 +532,69 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -419,7 +604,13 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFCCCCFF"/>
+      <color rgb="FFCC99FF"/>
+      <color rgb="FF9966FF"/>
+      <color rgb="FF6600CC"/>
       <color rgb="FFFFCCFF"/>
+      <color rgb="FFFF66FF"/>
+      <color rgb="FFFF33CC"/>
     </mruColors>
   </colors>
   <extLst>
@@ -729,6 +920,65 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E880B6FB-465A-4EAA-B0E7-5B64ED8EE870}">
+  <sheetPr>
+    <tabColor rgb="FF6600CC"/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="61.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="53.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="5"/>
+    </row>
+    <row r="2" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AAE0A43-D9F4-4772-8EF4-455A5F157D98}">
   <sheetPr>
     <tabColor theme="4"/>
@@ -737,9 +987,9 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.90625" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.54296875" style="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="61.36328125" style="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.90625" style="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.54296875" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="61.36328125" style="17" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.6328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.1796875" bestFit="1" customWidth="1"/>
   </cols>
@@ -765,60 +1015,60 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="21" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="20"/>
-      <c r="B3" s="24" t="s">
+      <c r="A3" s="37"/>
+      <c r="B3" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="20"/>
-      <c r="B4" s="24" t="s">
+      <c r="A4" s="37"/>
+      <c r="B4" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="23"/>
+      <c r="F4" s="22"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="20"/>
-      <c r="B5" s="24" t="s">
+      <c r="A5" s="37"/>
+      <c r="B5" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="21"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="23"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -836,7 +1086,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC3E1799-8E9C-484C-98AD-CB385F3A2068}">
   <sheetPr>
     <tabColor theme="5"/>
@@ -884,10 +1134,10 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="25" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="7" t="s">
@@ -899,18 +1149,18 @@
       <c r="E2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
     </row>
     <row r="3" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="12"/>
-      <c r="B3" s="13"/>
+      <c r="A3" s="42"/>
+      <c r="B3" s="25"/>
       <c r="C3" s="7" t="s">
         <v>5</v>
       </c>
@@ -920,61 +1170,77 @@
       <c r="E3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="16"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="12"/>
-      <c r="B4" s="13"/>
+      <c r="I3" s="14"/>
+    </row>
+    <row r="4" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="42"/>
+      <c r="B4" s="25"/>
       <c r="C4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="12"/>
-      <c r="B5" s="13" t="s">
+      <c r="D4" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+    </row>
+    <row r="5" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="42"/>
+      <c r="B5" s="25" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
+      <c r="D5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="12"/>
-      <c r="B6" s="13"/>
+      <c r="A6" s="42"/>
+      <c r="B6" s="25"/>
       <c r="C6" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="9"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
     </row>
     <row r="7" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="12"/>
-      <c r="B7" s="13" t="s">
+      <c r="A7" s="42"/>
+      <c r="B7" s="25" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="7" t="s">
@@ -986,18 +1252,18 @@
       <c r="E7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
     </row>
     <row r="8" spans="1:9" ht="58" x14ac:dyDescent="0.35">
-      <c r="A8" s="12"/>
-      <c r="B8" s="13"/>
+      <c r="A8" s="42"/>
+      <c r="B8" s="25"/>
       <c r="C8" s="7" t="s">
         <v>16</v>
       </c>
@@ -1007,18 +1273,18 @@
       <c r="E8" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
     </row>
     <row r="9" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="12"/>
-      <c r="B9" s="13"/>
+      <c r="A9" s="42"/>
+      <c r="B9" s="25"/>
       <c r="C9" s="7" t="s">
         <v>17</v>
       </c>
@@ -1028,17 +1294,17 @@
       <c r="E9" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
     </row>
     <row r="10" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="12"/>
+      <c r="A10" s="42"/>
       <c r="B10" s="6" t="s">
         <v>14</v>
       </c>
@@ -1048,19 +1314,19 @@
       <c r="D10" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="H10" s="18" t="s">
+      <c r="H10" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I10" s="16"/>
+      <c r="I10" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1073,14 +1339,146 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1FCA5BB-BB75-4692-B0DF-C8BE087A85D5}">
   <sheetPr>
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.08984375" style="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.54296875" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="44.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="43"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="30" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="43"/>
+      <c r="B4" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="29"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="43"/>
+      <c r="B5" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" s="32" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDEB6EE1-42EF-4269-A637-8062C94C1FEE}">
+  <sheetPr>
+    <tabColor rgb="FFFF33CC"/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="57.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="32" t="s">
+        <v>59</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/backend/aws/info.xlsx
+++ b/backend/aws/info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucia\Documents\GitHub\TFG_Posdata\backend\aws\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677EFA6E-5CD0-4B8B-9270-74E54C710522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50A46332-4E8C-4462-B992-46909EEBB2A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{717247B1-5BD0-4CA7-8E56-C22B8892B153}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{717247B1-5BD0-4CA7-8E56-C22B8892B153}"/>
   </bookViews>
   <sheets>
     <sheet name="API Gateway" sheetId="5" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="73">
   <si>
     <t>AWS Service</t>
   </si>
@@ -464,7 +464,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -523,7 +523,44 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -538,11 +575,11 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -550,8 +587,8 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -559,42 +596,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -605,9 +608,9 @@
   <colors>
     <mruColors>
       <color rgb="FFCCCCFF"/>
+      <color rgb="FF6600CC"/>
       <color rgb="FFCC99FF"/>
       <color rgb="FF9966FF"/>
-      <color rgb="FF6600CC"/>
       <color rgb="FFFFCCFF"/>
       <color rgb="FFFF66FF"/>
       <color rgb="FFFF33CC"/>
@@ -954,19 +957,19 @@
       <c r="F1" s="5"/>
     </row>
     <row r="2" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="C2" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="41" t="s">
+      <c r="D2" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="26" t="s">
         <v>71</v>
       </c>
       <c r="F2" s="11" t="s">
@@ -1015,60 +1018,60 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="33" t="s">
         <v>34</v>
       </c>
       <c r="B2" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="34" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="37"/>
+      <c r="A3" s="33"/>
       <c r="B3" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="37"/>
+      <c r="A4" s="33"/>
       <c r="B4" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="22"/>
+      <c r="F4" s="35"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="37"/>
+      <c r="A5" s="33"/>
       <c r="B5" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="22"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -1101,7 +1104,7 @@
     <col min="5" max="5" width="70.90625" style="3" customWidth="1"/>
     <col min="6" max="6" width="16.08984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.35">
@@ -1134,10 +1137,10 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="39" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="7" t="s">
@@ -1159,8 +1162,8 @@
       <c r="I2" s="14"/>
     </row>
     <row r="3" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="42"/>
-      <c r="B3" s="25"/>
+      <c r="A3" s="38"/>
+      <c r="B3" s="39"/>
       <c r="C3" s="7" t="s">
         <v>5</v>
       </c>
@@ -1182,8 +1185,8 @@
       <c r="I3" s="14"/>
     </row>
     <row r="4" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="42"/>
-      <c r="B4" s="25"/>
+      <c r="A4" s="38"/>
+      <c r="B4" s="39"/>
       <c r="C4" s="7" t="s">
         <v>8</v>
       </c>
@@ -1203,8 +1206,8 @@
       <c r="I4" s="14"/>
     </row>
     <row r="5" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="42"/>
-      <c r="B5" s="25" t="s">
+      <c r="A5" s="38"/>
+      <c r="B5" s="39" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="7" t="s">
@@ -1226,8 +1229,8 @@
       <c r="I5" s="14"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="42"/>
-      <c r="B6" s="25"/>
+      <c r="A6" s="38"/>
+      <c r="B6" s="39"/>
       <c r="C6" s="7" t="s">
         <v>11</v>
       </c>
@@ -1239,8 +1242,8 @@
       <c r="I6" s="13"/>
     </row>
     <row r="7" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="42"/>
-      <c r="B7" s="25" t="s">
+      <c r="A7" s="38"/>
+      <c r="B7" s="39" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="7" t="s">
@@ -1258,12 +1261,14 @@
       <c r="G7" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="14"/>
+      <c r="H7" s="45" t="s">
+        <v>68</v>
+      </c>
       <c r="I7" s="14"/>
     </row>
     <row r="8" spans="1:9" ht="58" x14ac:dyDescent="0.35">
-      <c r="A8" s="42"/>
-      <c r="B8" s="25"/>
+      <c r="A8" s="38"/>
+      <c r="B8" s="39"/>
       <c r="C8" s="7" t="s">
         <v>16</v>
       </c>
@@ -1279,12 +1284,14 @@
       <c r="G8" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="H8" s="14"/>
+      <c r="H8" s="45" t="s">
+        <v>68</v>
+      </c>
       <c r="I8" s="14"/>
     </row>
     <row r="9" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="42"/>
-      <c r="B9" s="25"/>
+      <c r="A9" s="38"/>
+      <c r="B9" s="39"/>
       <c r="C9" s="7" t="s">
         <v>17</v>
       </c>
@@ -1300,11 +1307,13 @@
       <c r="G9" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="H9" s="14"/>
+      <c r="H9" s="45" t="s">
+        <v>68</v>
+      </c>
       <c r="I9" s="14"/>
     </row>
     <row r="10" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="42"/>
+      <c r="A10" s="38"/>
       <c r="B10" s="6" t="s">
         <v>14</v>
       </c>
@@ -1348,8 +1357,8 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.08984375" style="26" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.54296875" style="26" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.08984375" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.54296875" style="20" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="30.36328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="44.36328125" bestFit="1" customWidth="1"/>
   </cols>
@@ -1372,16 +1381,16 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="23" t="s">
         <v>52</v>
       </c>
       <c r="E2" s="12" t="s">
@@ -1389,39 +1398,39 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="43"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="29" t="s">
+      <c r="A3" s="42"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="43" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="43"/>
-      <c r="B4" s="33" t="s">
+      <c r="A4" s="42"/>
+      <c r="B4" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="29"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="43"/>
-      <c r="B5" s="33" t="s">
+      <c r="A5" s="42"/>
+      <c r="B5" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="23" t="s">
         <v>56</v>
       </c>
     </row>
@@ -1465,16 +1474,16 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="23" t="s">
         <v>59</v>
       </c>
     </row>
